--- a/ABA_mining/outputs/eval/task3/price/llama3.2/contrary_v5/EVAL_SUMMARY.xlsx
+++ b/ABA_mining/outputs/eval/task3/price/llama3.2/contrary_v5/EVAL_SUMMARY.xlsx
@@ -541,16 +541,16 @@
         <v>27</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9232673267326733</v>
+        <v>0.9232669999999999</v>
       </c>
       <c r="M2" t="n">
         <v>0.9325</v>
       </c>
       <c r="N2" t="n">
-        <v>0.927860696517413</v>
+        <v>0.927861</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8725274725274725</v>
+        <v>0.8725270000000001</v>
       </c>
     </row>
     <row r="3">
@@ -600,16 +600,16 @@
         <v>28</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.923077</v>
       </c>
       <c r="M3" t="n">
         <v>0.93</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9265255292652554</v>
+        <v>0.926526</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8703296703296703</v>
+        <v>0.87033</v>
       </c>
     </row>
     <row r="4">
@@ -659,16 +659,16 @@
         <v>28</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.923077</v>
       </c>
       <c r="M4" t="n">
         <v>0.93</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9265255292652554</v>
+        <v>0.926526</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8703296703296703</v>
+        <v>0.87033</v>
       </c>
     </row>
   </sheetData>
@@ -784,16 +784,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.9231404958677686</v>
+        <v>0.92314</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9308333333333333</v>
+        <v>0.930833</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9269709543568465</v>
+        <v>0.926971</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8710622710622711</v>
+        <v>0.871062</v>
       </c>
       <c r="J2" t="n">
         <v>1365</v>
